--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1219-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1219-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21FA8AE4-5D0D-4E16-9781-88A86774BE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ACE99FE-F551-4928-9E9C-6B22D8FCACA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D2CDAF58-3497-41BA-8377-52A53480A496}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2991F408-D348-4519-9DD8-C239ACE467EB}"/>
   </bookViews>
   <sheets>
     <sheet name="1219-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1616,27 +1616,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002FA7AE-050D-45D0-A839-87AA569C5173}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7D5FAD-EA45-4270-890C-ADE476CD2A2C}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1670,7 +1670,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1706,7 +1706,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1826,7 +1826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="41">
         <v>2023</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2022</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <v>2021</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2020</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2019</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2018</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2017</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2016</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2015</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2014</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2013</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="43">
         <v>2012</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="45"/>
       <c r="B25" s="46"/>
       <c r="C25" s="20" t="s">
@@ -3308,7 +3308,7 @@
       <c r="W25" s="52"/>
       <c r="X25" s="48"/>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2011</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2010</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53">
         <v>2009</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="55"/>
       <c r="B29" s="56"/>
       <c r="C29" s="22" t="s">
@@ -3552,7 +3552,7 @@
       <c r="W29" s="62"/>
       <c r="X29" s="58"/>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2008</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="53">
         <v>2007</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>9.98</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="55"/>
       <c r="B32" s="56"/>
       <c r="C32" s="22" t="s">
@@ -3724,7 +3724,7 @@
       <c r="W32" s="62"/>
       <c r="X32" s="58"/>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>2006</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>2005</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2004</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>2003</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>2002</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>2001</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>2000</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>1999</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1998</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>1997</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1996</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>1995</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="43">
         <v>1994</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="45"/>
       <c r="B46" s="46"/>
       <c r="C46" s="20" t="s">
@@ -4688,7 +4688,7 @@
       <c r="W46" s="52"/>
       <c r="X46" s="48"/>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>1993</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1992</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>1991</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>1990</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="41">
         <v>1989</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>1988</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="41">
         <v>1987</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="39">
         <v>1985</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="41" t="s">
         <v>69</v>
       </c>
